--- a/採用管理ツール/採用管理ツール_2026.xlsx
+++ b/採用管理ツール/採用管理ツール_2026.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">応募者管理2026!$A$3:$T$3</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -9958,7 +9958,7 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="str">
-        <f aca="false">"目標200件に対し " &amp; TEXT(C5/200,"0.0%")</f>
+        <f aca="false">"目標200件に対し " &amp; TEXT(A5/200,"0.0%")</f>
         <v>目標200件に対し 0.0%</v>
       </c>
       <c r="B6" s="13"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13" t="str">
-        <f aca="false">"中期目標5名(各事業部1名)に対し " &amp; TEXT(N5/5,"0.0%")</f>
+        <f aca="false">"中期目標5名(各事業部1名)に対し " &amp; TEXT(K5/5,"0.0%")</f>
         <v>中期目標5名(各事業部1名)に対し 0.0%</v>
       </c>
       <c r="L6" s="13"/>
